--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2346C0BD-0F81-4F1A-A4DB-CF23F4E90875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15560"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="119">
   <si>
     <t>##</t>
   </si>
@@ -119,7 +125,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>데모</t>
     </r>
@@ -135,7 +141,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>프로그램</t>
     </r>
@@ -163,7 +169,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Courier New"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> Game Framework </t>
     </r>
@@ -194,7 +200,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Courier New"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> Game Framework </t>
     </r>
@@ -222,7 +228,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Courier New"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve"> Game Framework </t>
     </r>
@@ -239,7 +245,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Courier New"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>.</t>
     </r>
@@ -256,7 +262,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Courier New"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>.</t>
     </r>
@@ -353,7 +359,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>는</t>
     </r>
@@ -369,7 +375,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>유니티</t>
     </r>
@@ -385,7 +391,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>엔진</t>
     </r>
@@ -402,7 +408,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>버전을</t>
     </r>
@@ -418,7 +424,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>이용한</t>
     </r>
@@ -434,7 +440,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>게임</t>
     </r>
@@ -450,7 +456,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>시스템</t>
     </r>
@@ -466,7 +472,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>입니다</t>
     </r>
@@ -483,7 +489,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>주로</t>
     </r>
@@ -499,7 +505,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>게임</t>
     </r>
@@ -515,7 +521,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>개발과정에서</t>
     </r>
@@ -531,7 +537,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>자주</t>
     </r>
@@ -547,7 +553,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>사용하는</t>
     </r>
@@ -563,7 +569,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>모듈을</t>
     </r>
@@ -579,7 +585,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>캡슐화</t>
     </r>
@@ -595,7 +601,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>하여</t>
     </r>
@@ -611,7 +617,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>개발</t>
     </r>
@@ -627,7 +633,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>과정을</t>
     </r>
@@ -643,7 +649,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>규범화</t>
     </r>
@@ -659,7 +665,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>하고</t>
     </r>
@@ -675,7 +681,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>개발</t>
     </r>
@@ -691,7 +697,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>속도를</t>
     </r>
@@ -707,7 +713,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>높이며</t>
     </r>
@@ -723,7 +729,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>게임의</t>
     </r>
@@ -739,7 +745,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>콜리티를</t>
     </r>
@@ -755,7 +761,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>보장해</t>
     </r>
@@ -771,7 +777,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>드릴</t>
     </r>
@@ -787,7 +793,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>수</t>
     </r>
@@ -803,7 +809,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>있습니다</t>
     </r>
@@ -945,7 +951,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Courier New"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>?</t>
     </r>
@@ -1006,7 +1012,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Courier New"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>?</t>
     </r>
@@ -1067,7 +1073,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="MS Gothic"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t>효과음</t>
     </r>
@@ -1134,19 +1140,17 @@
   </si>
   <si>
     <t>1测试</t>
+  </si>
+  <si>
+    <t>/apple_bad</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1161,153 +1165,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Courier New"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1317,204 +1177,32 @@
     <font>
       <sz val="11"/>
       <name val="MS Gothic"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1522,251 +1210,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1774,68 +1220,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2093,511 +1495,526 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="16.8" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.83035714285714" style="1"/>
-    <col min="2" max="2" width="23.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6696428571429" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83035714285714" style="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:6">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:6">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:6" ht="14.5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:6">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:6" ht="14.5">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:6">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="1:6" ht="14.5">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="1:6">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:6">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>110</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
-      <c r="B27" s="1" t="s">
+    <row r="27" spans="1:6">
+      <c r="B27" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="2:3">
-      <c r="B28" s="1" t="s">
+    <row r="28" spans="1:6">
+      <c r="B28" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="2:3">
-      <c r="B29" s="1" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>117</v>
       </c>
     </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -1,39 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2346C0BD-0F81-4F1A-A4DB-CF23F4E90875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADB9CAF-9482-4D74-9895-D930C38199DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="~未翻译的文本" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="133">
   <si>
     <t>##</t>
   </si>
@@ -1144,13 +1132,60 @@
   <si>
     <t>/apple_bad</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>背包</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Btm_Map</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>Btm_Bag</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bag</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Btm_Do</t>
+  </si>
+  <si>
+    <t>修炼</t>
+  </si>
+  <si>
+    <t>Btm_Skill</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>Btm_Home</t>
+  </si>
+  <si>
+    <t>洞府</t>
+  </si>
+  <si>
+    <t>Btm_Fac</t>
+  </si>
+  <si>
+    <t>宗门</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1193,21 +1228,63 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1216,7 +1293,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1226,6 +1303,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1254,39 +1335,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1319,9 +1400,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1354,6 +1452,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1415,13 +1530,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1430,6 +1538,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1494,14 +1609,39 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2012,9 +2152,115 @@
         <v>111</v>
       </c>
     </row>
+    <row r="31" spans="1:6">
+      <c r="B31" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="14.5">
+      <c r="B33" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="14.5">
+      <c r="B34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="14.5">
+      <c r="B35" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="14.5">
+      <c r="B36" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="14.5">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="14.5">
+      <c r="A2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="14.5">
+      <c r="A3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="14.5">
+      <c r="A4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.5">
+      <c r="A5" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADB9CAF-9482-4D74-9895-D930C38199DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BBFD10-3FB0-4F28-85CB-EB1CE18F4F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="157">
   <si>
     <t>##</t>
   </si>
@@ -1179,13 +1179,110 @@
   </si>
   <si>
     <t>宗门</t>
+  </si>
+  <si>
+    <t>Level_0_0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level_0_1</t>
+  </si>
+  <si>
+    <t>Level_0_2</t>
+  </si>
+  <si>
+    <t>Level_1_0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level_1_1</t>
+  </si>
+  <si>
+    <t>Level_1_2</t>
+  </si>
+  <si>
+    <t>Level_2_0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level_2_1</t>
+  </si>
+  <si>
+    <t>Level_2_2</t>
+  </si>
+  <si>
+    <t>Level_3_0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level_3_1</t>
+  </si>
+  <si>
+    <t>Level_3_2</t>
+  </si>
+  <si>
+    <t>练气初期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>练气中期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>练气巅峰</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>筑基初期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>筑基中期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>筑基巅峰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>金丹初期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>金丹中期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>金丹巅峰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>元婴初期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>元婴中期</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>元婴巅峰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1247,6 +1344,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1293,7 +1397,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1307,6 +1411,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1641,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2206,10 +2312,106 @@
         <v>132</v>
       </c>
     </row>
+    <row r="37" spans="2:3" ht="14.5">
+      <c r="B37" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="14.5">
+      <c r="B38" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="14.5">
+      <c r="B39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="14.5">
+      <c r="B40" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="14.5">
+      <c r="B41" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="14.5">
+      <c r="B42" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="14.5">
+      <c r="B43" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="14.5">
+      <c r="B44" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="14.5">
+      <c r="B45" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="14.5">
+      <c r="B46" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="14.5">
+      <c r="B47" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" ht="14.5">
+      <c r="B48" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BBFD10-3FB0-4F28-85CB-EB1CE18F4F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0361F666-8B83-4CA8-B965-076A14C0CC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="~未翻译的文本" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullPrecision="0" calcOnSave="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="163">
   <si>
     <t>##</t>
   </si>
@@ -1276,13 +1276,31 @@
   <si>
     <t>元婴巅峰</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>GMap</t>
+  </si>
+  <si>
+    <t>密林</t>
+  </si>
+  <si>
+    <t>SMap</t>
+  </si>
+  <si>
+    <t>洞穴</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
+    <t>坊市</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1332,12 +1350,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
@@ -1352,7 +1364,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1361,11 +1373,6 @@
     </fill>
     <fill>
       <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1393,11 +1400,11 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1407,12 +1414,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1747,7 +1751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2281,47 +2285,47 @@
       </c>
     </row>
     <row r="33" spans="2:3" ht="14.5">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14.5">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14.5">
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="14.5">
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="14.5">
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="14.5">
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2329,23 +2333,23 @@
       </c>
     </row>
     <row r="39" spans="2:3" ht="14.5">
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="14.5">
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="14.5">
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -2353,15 +2357,15 @@
       </c>
     </row>
     <row r="42" spans="2:3" ht="14.5">
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="43" spans="2:3" ht="14.5">
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>139</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -2369,7 +2373,7 @@
       </c>
     </row>
     <row r="44" spans="2:3" ht="14.5">
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>140</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -2377,7 +2381,7 @@
       </c>
     </row>
     <row r="45" spans="2:3" ht="14.5">
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>141</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -2385,7 +2389,7 @@
       </c>
     </row>
     <row r="46" spans="2:3" ht="14.5">
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -2393,7 +2397,7 @@
       </c>
     </row>
     <row r="47" spans="2:3" ht="14.5">
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -2401,68 +2405,83 @@
       </c>
     </row>
     <row r="48" spans="2:3" ht="14.5">
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>144</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3">
+      <c r="B51" t="s">
+        <v>161</v>
+      </c>
+      <c r="C51" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.5">
-      <c r="A2" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="14.5">
-      <c r="A3" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="14.5">
-      <c r="A4" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="14.5">
-      <c r="A5" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>132</v>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0361F666-8B83-4CA8-B965-076A14C0CC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F052F67-DCA1-4BF7-8C71-9367A2EDCEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="170">
   <si>
     <t>##</t>
   </si>
@@ -1294,6 +1294,30 @@
   </si>
   <si>
     <t>坊市</t>
+  </si>
+  <si>
+    <t>ShopTab0</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>ShopTab1</t>
+  </si>
+  <si>
+    <t>ShopTab2</t>
+  </si>
+  <si>
+    <t>丹药</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>功法</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1751,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2434,6 +2458,30 @@
       </c>
       <c r="C51" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3">
+      <c r="B53" t="s">
+        <v>165</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3">
+      <c r="B54" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2458,26 +2506,26 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F052F67-DCA1-4BF7-8C71-9367A2EDCEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DFE264-A487-42F7-BB65-D08D66A2EF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5550" yWindow="2240" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="~未翻译的文本" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" fullPrecision="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="0" fullPrecision="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="193">
   <si>
     <t>##</t>
   </si>
@@ -63,6 +63,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -72,6 +73,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>演示程序</t>
@@ -85,6 +87,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -94,6 +97,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>演示程式</t>
@@ -104,6 +108,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -121,6 +126,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -148,6 +154,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -165,6 +172,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -179,6 +187,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -196,6 +205,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -207,6 +217,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -224,6 +235,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -241,6 +253,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -263,6 +276,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -272,6 +286,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>是基于</t>
@@ -280,6 +295,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -289,6 +305,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>引擎的游戏框架，主要对游戏开发过程中常用模块进行了封装，很大程度地规范开发过程、加快开发速度并保证产品质量。</t>
@@ -302,6 +319,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -311,6 +329,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>是基於</t>
@@ -319,6 +338,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -328,6 +348,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>引擎的遊戲框架，主要對遊戲開發過程中常用模組進行了封裝，很大程度地規範開發過程、加快開發速度並保證產品品質。</t>
@@ -338,6 +359,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -355,6 +377,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -371,6 +394,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -387,6 +411,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -404,6 +429,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -420,6 +446,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -436,6 +463,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -452,6 +480,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -468,6 +497,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -485,6 +515,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -501,6 +532,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -517,6 +549,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -533,6 +566,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -549,6 +583,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -565,6 +600,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -581,6 +617,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -597,6 +634,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -613,6 +651,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -629,6 +668,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -645,6 +685,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -661,6 +702,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -677,6 +719,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -693,6 +736,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -709,6 +753,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -725,6 +770,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -741,6 +787,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -757,6 +804,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -773,6 +821,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -789,6 +838,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -805,6 +855,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -930,6 +981,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -991,6 +1043,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1052,6 +1105,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1317,6 +1371,87 @@
   </si>
   <si>
     <t>材料</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Sweep</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>横扫</t>
+  </si>
+  <si>
+    <t>Skill_Blood</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>流血</t>
+  </si>
+  <si>
+    <t>Skill_RuFood</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>践踏</t>
+  </si>
+  <si>
+    <t>Skill_Wind</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩</t>
+  </si>
+  <si>
+    <t>Skill_God</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>神罗天正</t>
+  </si>
+  <si>
+    <t>Skill_Wan</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>万象天引</t>
+  </si>
+  <si>
+    <t>Skill_RecBlood</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>回血</t>
+  </si>
+  <si>
+    <t>Skill_ThreeFire</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>三火球</t>
+  </si>
+  <si>
+    <t>Skill_SpeedUp</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>急速</t>
+  </si>
+  <si>
+    <t>Skill_FireCircle2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球术</t>
+  </si>
+  <si>
+    <t>Skill_BeRecBlood</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动回血</t>
+  </si>
+  <si>
+    <t>Skill_FireCircle</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1335,6 +1470,7 @@
     <font>
       <sz val="11"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1346,6 +1482,7 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1356,6 +1493,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1775,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2482,6 +2620,102 @@
       </c>
       <c r="C54" s="2" t="s">
         <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3">
+      <c r="B55" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C55" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C56" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C58" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3">
+      <c r="B59" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="B60" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="B61" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3">
+      <c r="B62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3">
+      <c r="B64" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C64" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DFE264-A487-42F7-BB65-D08D66A2EF03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30EFA6E-5C2C-4165-A588-DEBF0D503115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5550" yWindow="2240" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="195">
   <si>
     <t>##</t>
   </si>
@@ -1452,6 +1452,13 @@
   </si>
   <si>
     <t>Skill_FireCircle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Lvup</t>
+  </si>
+  <si>
+    <t>升级</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1913,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2716,6 +2723,14 @@
       </c>
       <c r="C66" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="B67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -8,20 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30EFA6E-5C2C-4165-A588-DEBF0D503115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B622675-4911-4639-BE9B-462FBB374EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5550" yWindow="2240" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="~未翻译的文本" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="~未翻译的文本" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" fullPrecision="0"/>
+  <calcPr calcId="191029" fullPrecision="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="248">
   <si>
     <t>##</t>
   </si>
@@ -1459,6 +1473,167 @@
   </si>
   <si>
     <t>升级</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop_Buy</t>
+  </si>
+  <si>
+    <t>购买</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚气草</t>
+  </si>
+  <si>
+    <t>凝露花</t>
+  </si>
+  <si>
+    <t>黄精根</t>
+  </si>
+  <si>
+    <t>青灵叶</t>
+  </si>
+  <si>
+    <t>赤阳果</t>
+  </si>
+  <si>
+    <t>寒霜草</t>
+  </si>
+  <si>
+    <t>回春藤</t>
+  </si>
+  <si>
+    <t>地灵芝</t>
+  </si>
+  <si>
+    <t>紫云花</t>
+  </si>
+  <si>
+    <t>金髓草</t>
+  </si>
+  <si>
+    <t>玄阴草</t>
+  </si>
+  <si>
+    <t>赤炎花</t>
+  </si>
+  <si>
+    <t>七叶灵芝</t>
+  </si>
+  <si>
+    <t>玉髓果</t>
+  </si>
+  <si>
+    <t>筑基果</t>
+  </si>
+  <si>
+    <t>龙血草</t>
+  </si>
+  <si>
+    <t>玄灵花</t>
+  </si>
+  <si>
+    <t>九叶金莲</t>
+  </si>
+  <si>
+    <t>天心草</t>
+  </si>
+  <si>
+    <t>化婴果</t>
+  </si>
+  <si>
+    <t>Item10001</t>
+  </si>
+  <si>
+    <t>Item10002</t>
+  </si>
+  <si>
+    <t>Item10003</t>
+  </si>
+  <si>
+    <t>Item10004</t>
+  </si>
+  <si>
+    <t>Item10005</t>
+  </si>
+  <si>
+    <t>Item10006</t>
+  </si>
+  <si>
+    <t>Item10007</t>
+  </si>
+  <si>
+    <t>Item10008</t>
+  </si>
+  <si>
+    <t>Item10009</t>
+  </si>
+  <si>
+    <t>Item10010</t>
+  </si>
+  <si>
+    <t>Item10011</t>
+  </si>
+  <si>
+    <t>Item10012</t>
+  </si>
+  <si>
+    <t>Item10013</t>
+  </si>
+  <si>
+    <t>Item10014</t>
+  </si>
+  <si>
+    <t>Item10015</t>
+  </si>
+  <si>
+    <t>Item10016</t>
+  </si>
+  <si>
+    <t>Item10017</t>
+  </si>
+  <si>
+    <t>Item10018</t>
+  </si>
+  <si>
+    <t>Item10019</t>
+  </si>
+  <si>
+    <t>Item10020</t>
+  </si>
+  <si>
+    <t>Item20001</t>
+  </si>
+  <si>
+    <t>玄铁飞剑</t>
+  </si>
+  <si>
+    <t>Item30001</t>
+  </si>
+  <si>
+    <t>培元丹</t>
+  </si>
+  <si>
+    <t>Item30002</t>
+  </si>
+  <si>
+    <t>凝血丹</t>
+  </si>
+  <si>
+    <t>Item40001</t>
+  </si>
+  <si>
+    <t>储物袋</t>
+  </si>
+  <si>
+    <t>Item50001</t>
+  </si>
+  <si>
+    <t>Item50002</t>
+  </si>
+  <si>
+    <t>三火球</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1573,7 +1748,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1586,6 +1761,9 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1920,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2733,6 +2911,14 @@
         <v>194</v>
       </c>
     </row>
+    <row r="68" spans="2:3">
+      <c r="B68" t="s">
+        <v>195</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2741,9 +2927,255 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001E542C-9FD5-4079-AB64-ED7CD3988BE8}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="21.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="B2" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
+        <v>241</v>
+      </c>
+      <c r="C24" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">

--- a/Design/Excel/Localization.xlsx
+++ b/Design/Excel/Localization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B622675-4911-4639-BE9B-462FBB374EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F01662-E3E1-4E9E-B532-8AEA4B0230F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="250">
   <si>
     <t>##</t>
   </si>
@@ -1634,6 +1634,14 @@
   </si>
   <si>
     <t>三火球</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bag_Sell</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖出</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2098,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="23.33203125" customWidth="1"/>
@@ -2917,6 +2925,14 @@
       </c>
       <c r="C68" s="2" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
